--- a/Documentos/Documentos Excel - Hojas de calculo/Formulas de referencia.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Formulas de referencia.xlsx
@@ -1538,7 +1538,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CE28EE21-F140-ECB7-B756-BEB343EB8B76}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE28EE21-F140-ECB7-B756-BEB343EB8B76}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1556,44 +1556,6 @@
         <a:xfrm>
           <a:off x="0" y="1600200"/>
           <a:ext cx="7144747" cy="2819794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>802044</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>81106</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5724525" y="7000875"/>
-          <a:ext cx="4840644" cy="3853006"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Documentos/Documentos Excel - Hojas de calculo/Formulas de referencia.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Formulas de referencia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="COINCIDIR" sheetId="19" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
   <si>
     <t>id_cliente</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>COINCIDIR</t>
-  </si>
-  <si>
-    <t>Promedio</t>
   </si>
   <si>
     <t>Bélgica</t>
@@ -1538,7 +1535,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE28EE21-F140-ECB7-B756-BEB343EB8B76}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CE28EE21-F140-ECB7-B756-BEB343EB8B76}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2120,67 +2117,67 @@
     </row>
     <row r="6" spans="1:6" ht="45">
       <c r="B6" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:2">
@@ -2221,7 +2218,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2229,22 +2226,22 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="B6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="H6" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2255,10 +2252,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="11">
         <v>6</v>
@@ -2273,10 +2270,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H8" s="11">
         <v>9</v>
@@ -2291,10 +2288,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H9" s="11">
         <v>7</v>
@@ -2309,10 +2306,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="H10" s="11">
         <v>10</v>
@@ -2327,10 +2324,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2341,10 +2338,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2355,10 +2352,10 @@
         <v>7</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2369,10 +2366,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2383,10 +2380,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2397,10 +2394,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -2411,10 +2408,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -2425,10 +2422,10 @@
         <v>8</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -2439,10 +2436,10 @@
         <v>7</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2454,7 +2451,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja4"/>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -2462,7 +2459,6 @@
     <col min="12" max="12" width="15.25" customWidth="1"/>
     <col min="14" max="14" width="16.875" customWidth="1"/>
     <col min="15" max="15" width="21.625" customWidth="1"/>
-    <col min="16" max="16" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30">
@@ -2481,18 +2477,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="3:16">
+    <row r="23" spans="3:15">
       <c r="N23" s="23" t="s">
         <v>0</v>
       </c>
       <c r="O23" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="P23" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16">
+    </row>
+    <row r="24" spans="3:15">
       <c r="C24" s="14" t="s">
         <v>0</v>
       </c>
@@ -2528,9 +2521,8 @@
         <v>Centro</v>
       </c>
       <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-    </row>
-    <row r="25" spans="3:16">
+    </row>
+    <row r="25" spans="3:15">
       <c r="C25" s="4">
         <v>1</v>
       </c>
@@ -2562,7 +2554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="3:16">
+    <row r="26" spans="3:15">
       <c r="C26" s="4">
         <v>2</v>
       </c>
@@ -2594,7 +2586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="3:16">
+    <row r="27" spans="3:15">
       <c r="C27" s="4">
         <v>3</v>
       </c>
@@ -2626,7 +2618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="3:16">
+    <row r="28" spans="3:15">
       <c r="C28" s="4">
         <v>4</v>
       </c>
@@ -2658,7 +2650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="3:16">
+    <row r="29" spans="3:15">
       <c r="C29" s="4">
         <v>5</v>
       </c>
@@ -2690,7 +2682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="3:16">
+    <row r="30" spans="3:15">
       <c r="C30" s="4">
         <v>6</v>
       </c>
@@ -2722,7 +2714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:16">
+    <row r="31" spans="3:15">
       <c r="C31" s="4">
         <v>7</v>
       </c>
@@ -2754,7 +2746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="3:16">
+    <row r="32" spans="3:15">
       <c r="C32" s="4">
         <v>8</v>
       </c>
